--- a/SPEC MyBook Pro H7.xlsx
+++ b/SPEC MyBook Pro H7.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MyBook PRO\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MyBook PRO\Desktop\axioo_b2g\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07183267-AC83-44AA-B287-58BFCF1BC7C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3189E90C-AFC8-47C7-9F82-BAE93FEE1789}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,9 +22,12 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="47">
   <si>
-    <r>
-      <rPr>
-        <sz val="8.5"/>
+    <t xml:space="preserve">MyBook Pro H7 </t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -34,7 +37,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="8.5"/>
+        <sz val="9"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -44,7 +47,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="8.5"/>
+        <sz val="9"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -54,7 +57,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="8.5"/>
+        <sz val="9"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -64,7 +67,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="8.5"/>
+        <sz val="9"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -74,7 +77,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="8.5"/>
+        <sz val="9"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -84,7 +87,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="8.5"/>
+        <sz val="9"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -94,7 +97,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="8.5"/>
+        <sz val="9"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -102,19 +105,12 @@
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-      </rPr>
-      <t>Intel® Iris® Plus Graphic 645</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="8.5"/>
+    <t>Intel® Iris® Plus Graphic 645</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -124,7 +120,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="8.5"/>
+        <sz val="9"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -134,7 +130,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="8.5"/>
+        <sz val="9"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -144,7 +140,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="8.5"/>
+        <sz val="9"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -154,7 +150,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="8.5"/>
+        <sz val="9"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -164,7 +160,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="8.5"/>
+        <sz val="9"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -174,7 +170,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="8.5"/>
+        <sz val="9"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -184,7 +180,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="8.5"/>
+        <sz val="9"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -194,7 +190,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="8.5"/>
+        <sz val="9"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -204,7 +200,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="8.5"/>
+        <sz val="9"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -214,7 +210,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="8.5"/>
+        <sz val="9"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -224,7 +220,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="8.5"/>
+        <sz val="9"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -234,7 +230,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="8.5"/>
+        <sz val="9"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -244,7 +240,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="8.5"/>
+        <sz val="9"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -254,7 +250,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="8.5"/>
+        <sz val="9"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -264,7 +260,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="8.5"/>
+        <sz val="9"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -274,7 +270,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="8.5"/>
+        <sz val="9"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -284,7 +280,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="8.5"/>
+        <sz val="9"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -294,7 +290,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="8.5"/>
+        <sz val="9"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -303,7 +299,7 @@
     <r>
       <rPr>
         <vertAlign val="subscript"/>
-        <sz val="8.5"/>
+        <sz val="9"/>
         <rFont val="Cambria Math"/>
         <family val="1"/>
       </rPr>
@@ -311,7 +307,7 @@
     </r>
     <r>
       <rPr>
-        <sz val="8.5"/>
+        <sz val="9"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -321,7 +317,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="8.5"/>
+        <sz val="9"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -331,7 +327,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="8.5"/>
+        <sz val="9"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -341,7 +337,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="8.5"/>
+        <sz val="9"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -351,7 +347,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="8.5"/>
+        <sz val="9"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -361,7 +357,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="8.5"/>
+        <sz val="9"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -371,7 +367,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="8.5"/>
+        <sz val="9"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -381,7 +377,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="8.5"/>
+        <sz val="9"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -391,7 +387,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="8.5"/>
+        <sz val="9"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -401,7 +397,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="8.5"/>
+        <sz val="9"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -411,7 +407,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="8.5"/>
+        <sz val="9"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -421,7 +417,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="8.5"/>
+        <sz val="9"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -431,7 +427,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="8.5"/>
+        <sz val="9"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -441,7 +437,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="8.5"/>
+        <sz val="9"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -451,7 +447,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="8.5"/>
+        <sz val="9"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -461,7 +457,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="8.5"/>
+        <sz val="9"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -469,19 +465,12 @@
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-      </rPr>
-      <t>332.6 x 229.0 x 21.5mm</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="8.5"/>
+    <t>332.6 x 229.0 x 21.5mm</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -491,15 +480,12 @@
   <si>
     <r>
       <rPr>
-        <sz val="8.5"/>
+        <sz val="9"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
       <t>1.42Kg</t>
     </r>
-  </si>
-  <si>
-    <t xml:space="preserve">MyBook Pro H7 </t>
   </si>
 </sst>
 </file>
@@ -514,26 +500,29 @@
       <charset val="204"/>
     </font>
     <font>
-      <sz val="8.5"/>
+      <sz val="9"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
-      <sz val="8"/>
-      <name val="Microsoft YaHei"/>
-    </font>
-    <font>
-      <sz val="8.5"/>
+      <sz val="9"/>
       <name val="Calibri"/>
       <family val="1"/>
     </font>
     <font>
-      <sz val="8"/>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="9"/>
       <name val="Microsoft YaHei"/>
       <family val="2"/>
     </font>
     <font>
       <vertAlign val="subscript"/>
-      <sz val="8.5"/>
+      <sz val="9"/>
       <name val="Cambria Math"/>
       <family val="1"/>
     </font>
@@ -573,45 +562,48 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -918,251 +910,252 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C29"/>
-  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="12" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14" style="3" customWidth="1"/>
-    <col min="2" max="2" width="52.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.5546875" customWidth="1"/>
+    <col min="1" max="1" width="14" style="13" customWidth="1"/>
+    <col min="2" max="2" width="52.6640625" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.5546875" style="4" customWidth="1"/>
+    <col min="4" max="16384" width="8.88671875" style="4"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="3"/>
+    </row>
+    <row r="2" spans="1:3" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2"/>
-    </row>
-    <row r="2" spans="1:3" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="C2" s="2"/>
+      <c r="C2" s="3"/>
     </row>
     <row r="3" spans="1:3" ht="11.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="7"/>
-      <c r="B3" s="8"/>
-      <c r="C3" s="2"/>
+      <c r="A3" s="6"/>
+      <c r="B3" s="7"/>
+      <c r="C3" s="3"/>
     </row>
     <row r="4" spans="1:3" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" s="5" t="s">
+      <c r="A4" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="2"/>
+      <c r="B4" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="3"/>
     </row>
     <row r="5" spans="1:3" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5" s="5" t="s">
+      <c r="A5" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="2"/>
+      <c r="B5" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="3"/>
     </row>
     <row r="6" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B6" s="9" t="s">
+      <c r="A6" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C6" s="1"/>
+      <c r="B6" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" s="9"/>
     </row>
     <row r="7" spans="1:3" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7" s="5" t="s">
+      <c r="A7" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C7" s="2"/>
+      <c r="B7" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" s="3"/>
     </row>
     <row r="8" spans="1:3" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B8" s="5" t="s">
+      <c r="A8" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C8" s="2"/>
+      <c r="B8" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8" s="3"/>
     </row>
     <row r="9" spans="1:3" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B9" s="5" t="s">
+      <c r="A9" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="2"/>
+      <c r="B9" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C9" s="3"/>
     </row>
     <row r="10" spans="1:3" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B10" s="5" t="s">
+      <c r="A10" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C10" s="2"/>
+      <c r="B10" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C10" s="3"/>
     </row>
     <row r="11" spans="1:3" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="B11" s="5" t="s">
+      <c r="A11" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C11" s="2"/>
+      <c r="B11" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C11" s="3"/>
     </row>
     <row r="12" spans="1:3" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="B12" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="C12" s="2"/>
+      <c r="B12" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C12" s="3"/>
     </row>
     <row r="13" spans="1:3" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="10"/>
-      <c r="B13" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="C13" s="2"/>
+      <c r="B13" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C13" s="3"/>
     </row>
     <row r="14" spans="1:3" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="B14" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="C14" s="2"/>
+      <c r="B14" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C14" s="3"/>
     </row>
     <row r="15" spans="1:3" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="11"/>
-      <c r="B15" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C15" s="2"/>
+      <c r="B15" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C15" s="3"/>
     </row>
     <row r="16" spans="1:3" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="11"/>
-      <c r="B16" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C16" s="2"/>
+      <c r="B16" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C16" s="3"/>
     </row>
     <row r="17" spans="1:3" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="11"/>
-      <c r="B17" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="C17" s="2"/>
+      <c r="B17" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C17" s="3"/>
     </row>
     <row r="18" spans="1:3" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="11"/>
       <c r="B18" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="C18" s="2"/>
+        <v>28</v>
+      </c>
+      <c r="C18" s="3"/>
     </row>
     <row r="19" spans="1:3" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="11"/>
-      <c r="B19" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="C19" s="2"/>
+      <c r="B19" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C19" s="3"/>
     </row>
     <row r="20" spans="1:3" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="11"/>
-      <c r="B20" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="C20" s="2"/>
+      <c r="B20" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C20" s="3"/>
     </row>
     <row r="21" spans="1:3" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="B21" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C21" s="2"/>
+      <c r="B21" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C21" s="3"/>
     </row>
     <row r="22" spans="1:3" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="10"/>
-      <c r="B22" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="C22" s="2"/>
+      <c r="B22" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C22" s="3"/>
     </row>
     <row r="23" spans="1:3" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="B23" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="C23" s="2"/>
+      <c r="B23" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C23" s="3"/>
     </row>
     <row r="24" spans="1:3" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="10"/>
-      <c r="B24" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="C24" s="2"/>
+      <c r="B24" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C24" s="3"/>
     </row>
     <row r="25" spans="1:3" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="B25" s="5" t="s">
+      <c r="A25" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C25" s="2"/>
+      <c r="B25" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C25" s="3"/>
     </row>
     <row r="26" spans="1:3" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="B26" s="5" t="s">
+      <c r="A26" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="C26" s="2"/>
+      <c r="B26" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C26" s="3"/>
     </row>
     <row r="27" spans="1:3" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="B27" s="5" t="s">
+      <c r="A27" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="C27" s="2"/>
+      <c r="B27" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C27" s="3"/>
     </row>
     <row r="28" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="B28" s="9" t="s">
+      <c r="A28" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="C28" s="1"/>
+      <c r="B28" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="C28" s="9"/>
     </row>
     <row r="29" spans="1:3" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="B29" s="5" t="s">
+      <c r="A29" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C29" s="2"/>
+      <c r="B29" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C29" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="4">
